--- a/docs/변경정리_260604.xlsx
+++ b/docs/변경정리_260604.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\J-Bridge-test\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B553637-ACD6-421D-8C85-3B251D64AFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E80B990-2531-435F-BD3F-F2884CDD0434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="変更정리" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="105">
   <si>
     <t>No</t>
   </si>
@@ -58,9 +58,6 @@
     <t>멘토도 관리자와 같은 표. 머리글 1줄로 정리하고 목표레벨·시험레벨·이해도테스트·진척률 칸 추가. 줄별 버튼 제거, 이름을 누르면 리포트로 이동.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -326,6 +323,236 @@
   </si>
   <si>
     <t>[</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이규진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 「（月次自動）」 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기존에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>).</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제목이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 「N1 漢字 170項目（月次自動）」 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -333,7 +560,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Meiryo UI"/>
@@ -350,6 +577,24 @@
       <sz val="8"/>
       <name val="BatangChe"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -394,12 +639,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -716,8 +967,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -727,7 +978,7 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,7 +1001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -766,275 +1017,275 @@
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1</v>
@@ -1048,13 +1299,19 @@
       <c r="G14" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
@@ -1071,410 +1328,542 @@
       <c r="G15" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+      <c r="H15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="126" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="189" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="189" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="126" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="189" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="C30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="C33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="E35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="G35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="C24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="C25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="189" x14ac:dyDescent="0.25">
-      <c r="C26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="C28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="C30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="3:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="C33" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="3:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="3:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C35" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="3:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>100</v>
+      <c r="H36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
